--- a/docs/reports/Test_Cases_EvMoto_Mobile.xlsx
+++ b/docs/reports/Test_Cases_EvMoto_Mobile.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Driver" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin Dashboard" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'User'!$A$1:$I$238</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Driver'!$A$1:$I$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Driver'!$A$1:$I$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Admin Dashboard'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13608,6 +13610,1111 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId299"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>300</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="300" name="Image 300" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId300"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>301</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="301" name="Image 301" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId301"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>302</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="302" name="Image 302" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId302"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>303</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="303" name="Image 303" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId303"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>304</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="304" name="Image 304" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId304"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>305</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="305" name="Image 305" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId305"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>306</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="306" name="Image 306" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId306"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>307</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="307" name="Image 307" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId307"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>308</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="308" name="Image 308" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId308"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>309</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="309" name="Image 309" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId309"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>310</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="310" name="Image 310" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId310"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>311</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="311" name="Image 311" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId311"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>312</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="312" name="Image 312" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId312"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>313</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="313" name="Image 313" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId313"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>314</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="314" name="Image 314" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId314"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>315</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="315" name="Image 315" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId315"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>316</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="316" name="Image 316" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId316"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>317</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="317" name="Image 317" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId317"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>318</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="318" name="Image 318" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId318"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>319</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="319" name="Image 319" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId319"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>320</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="320" name="Image 320" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId320"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>321</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="321" name="Image 321" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId321"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>322</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="322" name="Image 322" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId322"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>323</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="323" name="Image 323" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId323"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>324</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="324" name="Image 324" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId324"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>325</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="325" name="Image 325" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId325"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>326</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="326" name="Image 326" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId326"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>327</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="327" name="Image 327" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId327"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -24712,7 +25819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I300"/>
+  <dimension ref="A1:I328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -36250,7 +37357,7 @@
     <row r="284" ht="135" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>TC_DRV_RENT_PT_01</t>
+          <t>TC_DRV_BOOK_BG_01</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr"/>
@@ -36261,674 +37368,2609 @@
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
+          <t>Aplikasi Driver (82283737237 / PIN 1234) &amp; User (82146625856 / PIN 1234) aktif di Dev Golang (https://evmotodev.justkidding.app). Driver berstatus Online di Beranda siap menerima order.</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>1. Driver berstatus Online dan smartphone dalam kondisi standby background / membuka aplikasi lain
+2. Backend mem-broadcast pesanan baru (Order EVMoto Motor) dengan durasi bidding window 20 detik
+3. Driver membuka layar smartphone setelah jeda 5 detik standby
+4. Driver melakukan swipe/swap untuk menerima pesanan sebelum timer habis</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>Pop-up overlay tidak lenyap prematur dalam 3-5 detik, swipe terima orderan berhasil mengunci pesanan.</t>
+        </is>
+      </c>
+      <c r="G284" s="5" t="inlineStr"/>
+      <c r="H284" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr">
+        <is>
+          <t>Driver Booking &amp; Pricing Engine: Driver 82283737237, User 82146625856, PIN bypass 1234 di Dev Golang. Kalkulasi argo, platform fee 10%, waiting fee (grace 15m), kupon voucher subsidi, surcharge e-wallet 2%, dan cancellation fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="135" customHeight="1">
+      <c r="A285" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BOOK_BG_02</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="inlineStr"/>
+      <c r="C285" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D285" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver (82283737237 / PIN 1234) &amp; User (82146625856 / PIN 1234) aktif di Dev Golang (https://evmotodev.justkidding.app). Driver berstatus Online di Beranda siap menerima order.</t>
+        </is>
+      </c>
+      <c r="E285" s="8" t="inlineStr">
+        <is>
+          <t>1. Smartphone driver terkunci dalam mode layar mati (Deep Sleep / Screen OFF)
+2. Pesanan masuk diterima oleh BackgroundService driver saat layar mati
+3. Sistem wajib memvalidasi ketersediaan WakeLock dan Full-Screen Intent
+4. Grace Window Guard aktif: driver diberikan minimal 15 detik window efektif sejak layar ON</t>
+        </is>
+      </c>
+      <c r="F285" s="8" t="inlineStr">
+        <is>
+          <t>Sistem mencegah hangusnya window penawaran secara prematur (mencegah bug pop-up 3-5 detik lenyap).</t>
+        </is>
+      </c>
+      <c r="G285" s="10" t="inlineStr"/>
+      <c r="H285" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I285" s="8" t="inlineStr">
+        <is>
+          <t>Driver Booking &amp; Pricing Engine: Driver 82283737237, User 82146625856, PIN bypass 1234 di Dev Golang. Kalkulasi argo, platform fee 10%, waiting fee (grace 15m), kupon voucher subsidi, surcharge e-wallet 2%, dan cancellation fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="135" customHeight="1">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BOOK_BG_03</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr"/>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver (82283737237 / PIN 1234) &amp; User (82146625856 / PIN 1234) aktif di Dev Golang (https://evmotodev.justkidding.app). Driver berstatus Online di Beranda siap menerima order.</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>1. Order di-broadcast ke beberapa driver di sekitar lokasi penjemputan
+2. Driver B lebih cepat melakukan swipe/swap menerima orderan di detik ke-6
+3. Sistem mengirimkan event notifikasi pembatalan penawaran ke Driver A yang baru membuka layar
+4. Aplikasi Driver A menampilkan feedback transisi visual sebelum menutup overlay</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>Muncul feedback visual yang jelas dan sopan kepada driver, bukan pop-up yang mendadak lenyap tanpa jejak.</t>
+        </is>
+      </c>
+      <c r="G286" s="5" t="inlineStr"/>
+      <c r="H286" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I286" s="3" t="inlineStr">
+        <is>
+          <t>Driver Booking &amp; Pricing Engine: Driver 82283737237, User 82146625856, PIN bypass 1234 di Dev Golang. Kalkulasi argo, platform fee 10%, waiting fee (grace 15m), kupon voucher subsidi, surcharge e-wallet 2%, dan cancellation fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="135" customHeight="1">
+      <c r="A287" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BOOK_BG_04</t>
+        </is>
+      </c>
+      <c r="B287" s="8" t="inlineStr"/>
+      <c r="C287" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D287" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver (82283737237 / PIN 1234) &amp; User (82146625856 / PIN 1234) aktif di Dev Golang (https://evmotodev.justkidding.app). Driver berstatus Online di Beranda siap menerima order.</t>
+        </is>
+      </c>
+      <c r="E287" s="8" t="inlineStr">
+        <is>
+          <t>1. Aplikasi berjalan di latar belakang dan floating overlay window sedang aktif
+2. Pengguna membuka aplikasi dan memicu transisi AppLifecycleState: paused -&gt; resumed
+3. Sistem mempertahankan integritas floating window tanpa memicu closeOrderOverlay() prematur
+4. Overlay window tetap terpasang pada WindowManager Android hingga user swipe atau timeout habis</t>
+        </is>
+      </c>
+      <c r="F287" s="8" t="inlineStr">
+        <is>
+          <t>Overlay tetap stabil dan tidak ter-destroy akibat transisi window manager Android.</t>
+        </is>
+      </c>
+      <c r="G287" s="10" t="inlineStr"/>
+      <c r="H287" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I287" s="8" t="inlineStr">
+        <is>
+          <t>Driver Booking &amp; Pricing Engine: Driver 82283737237, User 82146625856, PIN bypass 1234 di Dev Golang. Kalkulasi argo, platform fee 10%, waiting fee (grace 15m), kupon voucher subsidi, surcharge e-wallet 2%, dan cancellation fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="135" customHeight="1">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_RENT_PT_01</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr"/>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E284" s="3" t="inlineStr">
+      <c r="E288" s="3" t="inlineStr">
         <is>
           <t>1. Driver baru (Fresh Driver) masuk ke menu Manajemen Kendaraan
 2. Status kendaraan menampilkan empty state belum memiliki kendaraan terdaftar
 3. Status toggle 'Hubungkan Akun' berada pada kondisi OFF (Belum Terhubung)</t>
         </is>
       </c>
-      <c r="F284" s="3" t="inlineStr">
+      <c r="F288" s="3" t="inlineStr">
         <is>
           <t>Tampil 'Saat ini belum tersedia kendaraan' dan toggle sakelar berada pada posisi mati (OFF).</t>
         </is>
       </c>
-      <c r="G284" s="5" t="inlineStr"/>
-      <c r="H284" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I284" s="3" t="inlineStr">
+      <c r="G288" s="5" t="inlineStr"/>
+      <c r="H288" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I288" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="285" ht="135" customHeight="1">
-      <c r="A285" s="7" t="inlineStr">
+    <row r="289" ht="135" customHeight="1">
+      <c r="A289" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_PT_02</t>
         </is>
       </c>
-      <c r="B285" s="8" t="inlineStr"/>
-      <c r="C285" s="9" t="inlineStr">
+      <c r="B289" s="8" t="inlineStr"/>
+      <c r="C289" s="9" t="inlineStr">
         <is>
           <t>Positive True</t>
         </is>
       </c>
-      <c r="D285" s="8" t="inlineStr">
+      <c r="D289" s="8" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E285" s="8" t="inlineStr">
+      <c r="E289" s="8" t="inlineStr">
         <is>
           <t>1. Existing driver tanpa motor membuka menu penautan armada ECGO
 2. Sistem mengonfirmasi status 'Berhasil Di Hubungkan' pada modul Super Apps</t>
         </is>
       </c>
-      <c r="F285" s="8" t="inlineStr">
+      <c r="F289" s="8" t="inlineStr">
         <is>
           <t>Unit motor sewa terhubung dan toggle berubah menjadi aktif (Terhubung).</t>
         </is>
       </c>
-      <c r="G285" s="10" t="inlineStr"/>
-      <c r="H285" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I285" s="8" t="inlineStr">
+      <c r="G289" s="10" t="inlineStr"/>
+      <c r="H289" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I289" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="286" ht="135" customHeight="1">
-      <c r="A286" s="2" t="inlineStr">
+    <row r="290" ht="135" customHeight="1">
+      <c r="A290" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_PT_03</t>
         </is>
       </c>
-      <c r="B286" s="3" t="inlineStr"/>
-      <c r="C286" s="4" t="inlineStr">
+      <c r="B290" s="3" t="inlineStr"/>
+      <c r="C290" s="4" t="inlineStr">
         <is>
           <t>Positive True</t>
         </is>
       </c>
-      <c r="D286" s="3" t="inlineStr">
+      <c r="D290" s="3" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E286" s="3" t="inlineStr">
+      <c r="E290" s="3" t="inlineStr">
         <is>
           <t>1. Kontrak Orphan Motor terverifikasi: unit lama tidak di-soft delete dan status backend menjadi 'ORPHAN'</t>
         </is>
       </c>
-      <c r="F286" s="3" t="inlineStr">
+      <c r="F290" s="3" t="inlineStr">
         <is>
           <t>Motor lama berstatus Orphan (tidak dihapus) dan plat nomor baru aktif di akun driver.</t>
         </is>
       </c>
-      <c r="G286" s="5" t="inlineStr"/>
-      <c r="H286" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I286" s="3" t="inlineStr">
+      <c r="G290" s="5" t="inlineStr"/>
+      <c r="H290" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I290" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="287" ht="135" customHeight="1">
-      <c r="A287" s="7" t="inlineStr">
+    <row r="291" ht="135" customHeight="1">
+      <c r="A291" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_PT_04</t>
         </is>
       </c>
-      <c r="B287" s="8" t="inlineStr"/>
-      <c r="C287" s="9" t="inlineStr">
+      <c r="B291" s="8" t="inlineStr"/>
+      <c r="C291" s="9" t="inlineStr">
         <is>
           <t>Positive True</t>
         </is>
       </c>
-      <c r="D287" s="8" t="inlineStr">
+      <c r="D291" s="8" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E287" s="8" t="inlineStr">
+      <c r="E291" s="8" t="inlineStr">
         <is>
           <t>1. Driver mengaktifkan integrasi akun cicilan sewa pada unit yang sama
 2. Status akun terhubung dengan kontrak cicilan ECGO tanpa mengubah nomor plat aktif</t>
         </is>
       </c>
-      <c r="F287" s="8" t="inlineStr">
+      <c r="F291" s="8" t="inlineStr">
         <is>
           <t>Penautan program cicilan berhasil tanpa mengubah data kendaraan aktif.</t>
         </is>
       </c>
-      <c r="G287" s="10" t="inlineStr"/>
-      <c r="H287" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I287" s="8" t="inlineStr">
+      <c r="G291" s="10" t="inlineStr"/>
+      <c r="H291" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I291" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="288" ht="135" customHeight="1">
-      <c r="A288" s="2" t="inlineStr">
+    <row r="292" ht="135" customHeight="1">
+      <c r="A292" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_PT_05</t>
         </is>
       </c>
-      <c r="B288" s="3" t="inlineStr"/>
-      <c r="C288" s="4" t="inlineStr">
+      <c r="B292" s="3" t="inlineStr"/>
+      <c r="C292" s="4" t="inlineStr">
         <is>
           <t>Positive True</t>
         </is>
       </c>
-      <c r="D288" s="3" t="inlineStr">
+      <c r="D292" s="3" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E288" s="3" t="inlineStr">
+      <c r="E292" s="3" t="inlineStr">
         <is>
           <t>1. Unit Orphan dapat dialihkan dan riwayat kepemilikan sebelumnya tetap tersimpan utuh</t>
         </is>
       </c>
-      <c r="F288" s="3" t="inlineStr">
+      <c r="F292" s="3" t="inlineStr">
         <is>
           <t>Unit Orphan berhasil di-reassign ke mitra baru tanpa kehilangan riwayat armada sebelumnya.</t>
         </is>
       </c>
-      <c r="G288" s="5" t="inlineStr"/>
-      <c r="H288" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I288" s="3" t="inlineStr">
+      <c r="G292" s="5" t="inlineStr"/>
+      <c r="H292" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I292" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="289" ht="135" customHeight="1">
-      <c r="A289" s="7" t="inlineStr">
+    <row r="293" ht="135" customHeight="1">
+      <c r="A293" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_PT_06</t>
         </is>
       </c>
-      <c r="B289" s="8" t="inlineStr"/>
-      <c r="C289" s="9" t="inlineStr">
+      <c r="B293" s="8" t="inlineStr"/>
+      <c r="C293" s="9" t="inlineStr">
         <is>
           <t>Positive True</t>
         </is>
       </c>
-      <c r="D289" s="8" t="inlineStr">
+      <c r="D293" s="8" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E289" s="8" t="inlineStr">
+      <c r="E293" s="8" t="inlineStr">
         <is>
           <t>1. Akun driver telah terhubung (Toggle Status = ON)
 2. Driver mencoba mengetuk switch toggle untuk memutus hubungan akun secara sepihak
 3. Sistem menegakkan aturan One-Way Binding: Sakelar terkunci atau dialog restriksi administrator ditampilkan</t>
         </is>
       </c>
-      <c r="F289" s="8" t="inlineStr">
+      <c r="F293" s="8" t="inlineStr">
         <is>
           <t>Switch berada dalam status disabled/locked, dan upaya klik menampilkan dialog pencegahan pemutusan sepihak.</t>
         </is>
       </c>
-      <c r="G289" s="10" t="inlineStr"/>
-      <c r="H289" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I289" s="8" t="inlineStr">
+      <c r="G293" s="10" t="inlineStr"/>
+      <c r="H293" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I293" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="290" ht="135" customHeight="1">
-      <c r="A290" s="2" t="inlineStr">
+    <row r="294" ht="135" customHeight="1">
+      <c r="A294" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_BL_01</t>
         </is>
       </c>
-      <c r="B290" s="3" t="inlineStr"/>
-      <c r="C290" s="4" t="inlineStr">
+      <c r="B294" s="3" t="inlineStr"/>
+      <c r="C294" s="4" t="inlineStr">
         <is>
           <t>Business Logic</t>
         </is>
       </c>
-      <c r="D290" s="3" t="inlineStr">
+      <c r="D294" s="3" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E290" s="3" t="inlineStr">
+      <c r="E294" s="3" t="inlineStr">
         <is>
           <t>1. Driver menginisiasi proses linking akun
 2. State UI melakukan rollback otomatis ke posisi OFF untuk mencegah desinkronisasi data</t>
         </is>
       </c>
-      <c r="F290" s="3" t="inlineStr">
+      <c r="F294" s="3" t="inlineStr">
         <is>
           <t>Status toggle dikembalikan ke posisi OFF dan saldo tidak mengalami pemotongan sepihak.</t>
         </is>
       </c>
-      <c r="G290" s="5" t="inlineStr"/>
-      <c r="H290" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I290" s="3" t="inlineStr">
+      <c r="G294" s="5" t="inlineStr"/>
+      <c r="H294" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I294" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="291" ht="135" customHeight="1">
-      <c r="A291" s="7" t="inlineStr">
+    <row r="295" ht="135" customHeight="1">
+      <c r="A295" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_BL_02</t>
         </is>
       </c>
-      <c r="B291" s="8" t="inlineStr"/>
-      <c r="C291" s="9" t="inlineStr">
+      <c r="B295" s="8" t="inlineStr"/>
+      <c r="C295" s="9" t="inlineStr">
         <is>
           <t>Business Logic</t>
         </is>
       </c>
-      <c r="D291" s="8" t="inlineStr">
+      <c r="D295" s="8" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E291" s="8" t="inlineStr">
+      <c r="E295" s="8" t="inlineStr">
         <is>
           <t>1. Sistem memverifikasi integritas basis data kendaraan dan riwayat odometer
 2. Riwayat pesanan masa lalu tersimpan rapi dan log kilometer terus bersambung</t>
         </is>
       </c>
-      <c r="F291" s="8" t="inlineStr">
+      <c r="F295" s="8" t="inlineStr">
         <is>
           <t>Data odometer dan order history unit tidak mengalami data corruption atau override.</t>
         </is>
       </c>
-      <c r="G291" s="10" t="inlineStr"/>
-      <c r="H291" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I291" s="8" t="inlineStr">
+      <c r="G295" s="10" t="inlineStr"/>
+      <c r="H295" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I295" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="292" ht="135" customHeight="1">
-      <c r="A292" s="2" t="inlineStr">
+    <row r="296" ht="135" customHeight="1">
+      <c r="A296" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_BL_03</t>
         </is>
       </c>
-      <c r="B292" s="3" t="inlineStr"/>
-      <c r="C292" s="4" t="inlineStr">
+      <c r="B296" s="3" t="inlineStr"/>
+      <c r="C296" s="4" t="inlineStr">
         <is>
           <t>Business Logic</t>
         </is>
       </c>
-      <c r="D292" s="3" t="inlineStr">
+      <c r="D296" s="3" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E292" s="3" t="inlineStr">
+      <c r="E296" s="3" t="inlineStr">
         <is>
           <t>1. Akun driver aktif dihubungkan pada perangkat utama
 2. Status toggle di perangkat sekunder ter-sinkronisasi realtime dalam posisi ON dan terkunci</t>
         </is>
       </c>
-      <c r="F292" s="3" t="inlineStr">
+      <c r="F296" s="3" t="inlineStr">
         <is>
           <t>Perangkat sekunder langsung menampilkan status ON/Terkunci tanpa inkonsistensi cache lokal.</t>
         </is>
       </c>
-      <c r="G292" s="5" t="inlineStr"/>
-      <c r="H292" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I292" s="3" t="inlineStr">
+      <c r="G296" s="5" t="inlineStr"/>
+      <c r="H296" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I296" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="293" ht="135" customHeight="1">
-      <c r="A293" s="7" t="inlineStr">
+    <row r="297" ht="135" customHeight="1">
+      <c r="A297" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NF_01</t>
         </is>
       </c>
-      <c r="B293" s="8" t="inlineStr"/>
-      <c r="C293" s="9" t="inlineStr">
+      <c r="B297" s="8" t="inlineStr"/>
+      <c r="C297" s="9" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D293" s="8" t="inlineStr">
+      <c r="D297" s="8" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E293" s="8" t="inlineStr">
+      <c r="E297" s="8" t="inlineStr">
         <is>
           <t>1. Permintaan pemutusan koneksi sepihak dikirim tanpa otorisasi Superadmin</t>
         </is>
       </c>
-      <c r="F293" s="8" t="inlineStr">
+      <c r="F297" s="8" t="inlineStr">
         <is>
           <t>Backend menolak request dengan status HTTP 403 Forbidden (kebijakan One-Way Binding ditegakkan).</t>
         </is>
       </c>
-      <c r="G293" s="10" t="inlineStr"/>
-      <c r="H293" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I293" s="8" t="inlineStr">
+      <c r="G297" s="10" t="inlineStr"/>
+      <c r="H297" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I297" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="294" ht="135" customHeight="1">
-      <c r="A294" s="2" t="inlineStr">
+    <row r="298" ht="135" customHeight="1">
+      <c r="A298" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NF_02</t>
         </is>
       </c>
-      <c r="B294" s="3" t="inlineStr"/>
-      <c r="C294" s="4" t="inlineStr">
+      <c r="B298" s="3" t="inlineStr"/>
+      <c r="C298" s="4" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D294" s="3" t="inlineStr">
+      <c r="D298" s="3" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E294" s="3" t="inlineStr">
+      <c r="E298" s="3" t="inlineStr">
         <is>
           <t>1. Sistem anti-fraud menolak penautan duplikat dan menampilkan peringatan konflik armada</t>
         </is>
       </c>
-      <c r="F294" s="3" t="inlineStr">
+      <c r="F298" s="3" t="inlineStr">
         <is>
           <t>Muncul notifikasi penolakan 'Kendaraan sedang digunakan oleh driver aktif lain'.</t>
         </is>
       </c>
-      <c r="G294" s="5" t="inlineStr"/>
-      <c r="H294" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I294" s="3" t="inlineStr">
+      <c r="G298" s="5" t="inlineStr"/>
+      <c r="H298" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I298" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="295" ht="135" customHeight="1">
-      <c r="A295" s="7" t="inlineStr">
+    <row r="299" ht="135" customHeight="1">
+      <c r="A299" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NF_03</t>
         </is>
       </c>
-      <c r="B295" s="8" t="inlineStr"/>
-      <c r="C295" s="9" t="inlineStr">
+      <c r="B299" s="8" t="inlineStr"/>
+      <c r="C299" s="9" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D295" s="8" t="inlineStr">
+      <c r="D299" s="8" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E295" s="8" t="inlineStr">
+      <c r="E299" s="8" t="inlineStr">
         <is>
           <t>1. Driver telah melepas motor lama menjadi unit berstatus Orphan
 2. Akses telemetri dibatasi sepenuhnya dan kontrol berpindah ke sistem sentral</t>
         </is>
       </c>
-      <c r="F295" s="8" t="inlineStr">
+      <c r="F299" s="8" t="inlineStr">
         <is>
           <t>Akses ditolak dan token telemetri kendaraan lama otomatis dicabut (revoked).</t>
         </is>
       </c>
-      <c r="G295" s="10" t="inlineStr"/>
-      <c r="H295" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I295" s="8" t="inlineStr">
+      <c r="G299" s="10" t="inlineStr"/>
+      <c r="H299" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I299" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="296" ht="135" customHeight="1">
-      <c r="A296" s="2" t="inlineStr">
+    <row r="300" ht="135" customHeight="1">
+      <c r="A300" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NT_01</t>
         </is>
       </c>
-      <c r="B296" s="3" t="inlineStr"/>
-      <c r="C296" s="4" t="inlineStr">
+      <c r="B300" s="3" t="inlineStr"/>
+      <c r="C300" s="4" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D296" s="3" t="inlineStr">
+      <c r="D300" s="3" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E296" s="3" t="inlineStr">
+      <c r="E300" s="3" t="inlineStr">
         <is>
           <t>1. Motor mitra mengalami kerusakan teknis darurat dan ditukar di bengkel resmi ECGO
 2. Mekanik mengesahkan berita acara pertukaran unit fisik di portal operasional
 3. Aplikasi Driver menyerap identitas unit baru secara otomatis tanpa membatalkan cicilan</t>
         </is>
       </c>
-      <c r="F296" s="3" t="inlineStr">
+      <c r="F300" s="3" t="inlineStr">
         <is>
           <t>Unit pengganti terhubung secara otomatis ke kontrak sewa aktif driver.</t>
         </is>
       </c>
-      <c r="G296" s="5" t="inlineStr"/>
-      <c r="H296" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I296" s="3" t="inlineStr">
+      <c r="G300" s="5" t="inlineStr"/>
+      <c r="H300" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I300" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="297" ht="135" customHeight="1">
-      <c r="A297" s="7" t="inlineStr">
+    <row r="301" ht="135" customHeight="1">
+      <c r="A301" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NT_02</t>
         </is>
       </c>
-      <c r="B297" s="8" t="inlineStr"/>
-      <c r="C297" s="9" t="inlineStr">
+      <c r="B301" s="8" t="inlineStr"/>
+      <c r="C301" s="9" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D297" s="8" t="inlineStr">
+      <c r="D301" s="8" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E297" s="8" t="inlineStr">
+      <c r="E301" s="8" t="inlineStr">
         <is>
           <t>1. Driver mengklik sakelar Hubungkan Akun
 2. Aplikasi menampilkan pesan timeout ramah pengguna dan opsi coba kembali tanpa error crash</t>
         </is>
       </c>
-      <c r="F297" s="8" t="inlineStr">
+      <c r="F301" s="8" t="inlineStr">
         <is>
           <t>Sistem menyajikan tombol 'Coba Lagi' tanpa menduplikasi data transaksi di backend.</t>
         </is>
       </c>
-      <c r="G297" s="10" t="inlineStr"/>
-      <c r="H297" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I297" s="8" t="inlineStr">
+      <c r="G301" s="10" t="inlineStr"/>
+      <c r="H301" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I301" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="298" ht="135" customHeight="1">
-      <c r="A298" s="2" t="inlineStr">
+    <row r="302" ht="135" customHeight="1">
+      <c r="A302" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NT_03</t>
         </is>
       </c>
-      <c r="B298" s="3" t="inlineStr"/>
-      <c r="C298" s="4" t="inlineStr">
+      <c r="B302" s="3" t="inlineStr"/>
+      <c r="C302" s="4" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D298" s="3" t="inlineStr">
+      <c r="D302" s="3" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E298" s="3" t="inlineStr">
+      <c r="E302" s="3" t="inlineStr">
         <is>
           <t>1. Driver belum mengaktifkan penautan akun cicilan (Status Unlinked)
 2. Driver mengakses menu aktivitas, dompet reguler, dan panduan pengemudi
 3. Aplikasi tetap berfungsi penuh dengan menampilkan kartu edukasi manfaat penautan armada</t>
         </is>
       </c>
-      <c r="F298" s="3" t="inlineStr">
+      <c r="F302" s="3" t="inlineStr">
         <is>
           <t>Aplikasi berjalan mulus dengan banner pengingat penautan akun tanpa memblokir operasional normal.</t>
         </is>
       </c>
-      <c r="G298" s="5" t="inlineStr"/>
-      <c r="H298" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I298" s="3" t="inlineStr">
+      <c r="G302" s="5" t="inlineStr"/>
+      <c r="H302" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I302" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="299" ht="135" customHeight="1">
-      <c r="A299" s="7" t="inlineStr">
+    <row r="303" ht="135" customHeight="1">
+      <c r="A303" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NT_04</t>
         </is>
       </c>
-      <c r="B299" s="8" t="inlineStr"/>
-      <c r="C299" s="9" t="inlineStr">
+      <c r="B303" s="8" t="inlineStr"/>
+      <c r="C303" s="9" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D299" s="8" t="inlineStr">
+      <c r="D303" s="8" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E299" s="8" t="inlineStr">
+      <c r="E303" s="8" t="inlineStr">
         <is>
           <t>1. Driver memicu proses verifikasi data kontrak sewa motor
 2. Sistem menolak penautan otomatis demi keamanan identitas dan pencegahan pemalsuan data</t>
         </is>
       </c>
-      <c r="F299" s="8" t="inlineStr">
+      <c r="F303" s="8" t="inlineStr">
         <is>
           <t>Penautan dibatalkan dan sistem meminta driver melakukan verifikasi KTP di kantor cabang.</t>
         </is>
       </c>
-      <c r="G299" s="10" t="inlineStr"/>
-      <c r="H299" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I299" s="8" t="inlineStr">
+      <c r="G303" s="10" t="inlineStr"/>
+      <c r="H303" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I303" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
-    <row r="300" ht="135" customHeight="1">
-      <c r="A300" s="2" t="inlineStr">
+    <row r="304" ht="135" customHeight="1">
+      <c r="A304" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NT_05</t>
         </is>
       </c>
-      <c r="B300" s="3" t="inlineStr"/>
-      <c r="C300" s="4" t="inlineStr">
+      <c r="B304" s="3" t="inlineStr"/>
+      <c r="C304" s="4" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D300" s="3" t="inlineStr">
+      <c r="D304" s="3" t="inlineStr">
         <is>
           <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
         </is>
       </c>
-      <c r="E300" s="3" t="inlineStr">
+      <c r="E304" s="3" t="inlineStr">
         <is>
           <t>1. Driver mencoba memindai QR code stasiun swap baterai ECGO di tengah jalan
 2. Sistem memblokir proses swap dan menginstruksikan driver mengantar penumpang ke tujuan terlebih dahulu</t>
         </is>
       </c>
-      <c r="F300" s="3" t="inlineStr">
+      <c r="F304" s="3" t="inlineStr">
         <is>
           <t>Muncul dialog peringatan untuk menyelesaikan pesanan terlebih dahulu sebelum melakukan penukaran baterai.</t>
         </is>
       </c>
-      <c r="G300" s="5" t="inlineStr"/>
-      <c r="H300" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I300" s="3" t="inlineStr">
+      <c r="G304" s="5" t="inlineStr"/>
+      <c r="H304" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I304" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Fitur pre-order stabil tanpa pesanan aktif.</t>
         </is>
       </c>
     </row>
+    <row r="305" ht="135" customHeight="1">
+      <c r="A305" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PT_01</t>
+        </is>
+      </c>
+      <c r="B305" s="8" t="inlineStr"/>
+      <c r="C305" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D305" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E305" s="8" t="inlineStr">
+        <is>
+          <t>1. Server mendispatch 3 order dalam satu batch ke aplikasi driver
+2. Aplikasi Driver menampilkan 3 tawaran order secara simultan</t>
+        </is>
+      </c>
+      <c r="F305" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver menampilkan seluruh kartu order dalam daftar (misal 3 order simultan) dengan rincian titik jemput, titik antar, dan perkiraan pendapatan.</t>
+        </is>
+      </c>
+      <c r="G305" s="10" t="inlineStr"/>
+      <c r="H305" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I305" s="8" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="135" customHeight="1">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PT_02</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr"/>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>1. Driver menerima tawaran pesanan dari jalur batch dispatch
+2. Memeriksa indikator timer pada seluruh kartu penawaran order
+3. Kartu order terkonfirmasi TIDAK MEMILIKI countdown timer</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>Field 'has_countdown' bernilai False dan tidak ada hitung mundur pada antarmuka order.</t>
+        </is>
+      </c>
+      <c r="G306" s="5" t="inlineStr"/>
+      <c r="H306" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I306" s="3" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="135" customHeight="1">
+      <c r="A307" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PT_03</t>
+        </is>
+      </c>
+      <c r="B307" s="8" t="inlineStr"/>
+      <c r="C307" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D307" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E307" s="8" t="inlineStr">
+        <is>
+          <t>1. Layar menampilkan 2 pilihan order batch yang tersedia
+2. Driver melakukan Swipe/Terima pada order ORD-PICK-A
+3. Order ORD-PICK-A berhasil diterima dan menjadi order aktif driver</t>
+        </is>
+      </c>
+      <c r="F307" s="8" t="inlineStr">
+        <is>
+          <t>Order terpilih berpindah ke status 'ACCEPTED', dan siklus penjemputan dimulai.</t>
+        </is>
+      </c>
+      <c r="G307" s="10" t="inlineStr"/>
+      <c r="H307" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I307" s="8" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="135" customHeight="1">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PT_04</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr"/>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>1. Batch dispatch mengirimkan kombinasi pesanan reguler dan terjadwal
+2. Memeriksa kategorisasi tipe order pada daftar
+3. Kedua tipe order terpisah secara kategoris</t>
+        </is>
+      </c>
+      <c r="F308" s="3" t="inlineStr">
+        <is>
+          <t>Order berkategori 'regular' ditandai sebagai 'Pesanan Reguler', sedangkan order berkategori 'advance' ditandai sebagai 'Advance Booking' (Pesanan Terjadwal).</t>
+        </is>
+      </c>
+      <c r="G308" s="5" t="inlineStr"/>
+      <c r="H308" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I308" s="3" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="135" customHeight="1">
+      <c r="A309" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PF_01</t>
+        </is>
+      </c>
+      <c r="B309" s="8" t="inlineStr"/>
+      <c r="C309" s="9" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D309" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E309" s="8" t="inlineStr">
+        <is>
+          <t>1. Batas kapasitas order bersamaan diatur menjadi 3 pesanan
+2. Driver menerima 3 pesanan berturut-turut
+3. Driver memegang tepat 3 pesanan aktif
+4. Upaya menerima pesanan ke-4 ditolak oleh sistem</t>
+        </is>
+      </c>
+      <c r="F309" s="8" t="inlineStr">
+        <is>
+          <t>Driver sukses memegang 3 order. Upaya menerima order ke-4 ditolak secara valid karena telah mencapai batas concurrent order.</t>
+        </is>
+      </c>
+      <c r="G309" s="10" t="inlineStr"/>
+      <c r="H309" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I309" s="8" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="135" customHeight="1">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PF_02</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr"/>
+      <c r="C310" s="4" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>1. Tawaran order batch tampil di layar
+2. Driver membiarkan tawaran terbuka selama simulasi beberapa waktu
+3. Tawaran order tetap aktif dan siap diambil kapan saja</t>
+        </is>
+      </c>
+      <c r="F310" s="3" t="inlineStr">
+        <is>
+          <t>Tawaran order tetap berstatus 'OFFERED' (tidak auto-expire atau menghilang sendiri).</t>
+        </is>
+      </c>
+      <c r="G310" s="5" t="inlineStr"/>
+      <c r="H310" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I310" s="3" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="135" customHeight="1">
+      <c r="A311" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PF_03</t>
+        </is>
+      </c>
+      <c r="B311" s="8" t="inlineStr"/>
+      <c r="C311" s="9" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D311" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E311" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver hanya memiliki penawaran pesanan tipe Reguler
+2. Memfilter daftar berdasarkan tipe 'advance'
+3. Daftar Advance Booking kosong dengan aman</t>
+        </is>
+      </c>
+      <c r="F311" s="8" t="inlineStr">
+        <is>
+          <t>Tab Advance Booking menampilkan state kosong secara aman tanpa error ('Belum Ada Pesanan Terjadwal').</t>
+        </is>
+      </c>
+      <c r="G311" s="10" t="inlineStr"/>
+      <c r="H311" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I311" s="8" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="135" customHeight="1">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NT_01</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr"/>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>1. Terdapat 2 order dalam daftar batch
+2. Driver menekan tombol 'Tolak' pada ORD-REJECT-ME
+3. Order ORD-REJECT-ME berhasil di-reject</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="inlineStr">
+        <is>
+          <t>Order tersebut dihapus dari daftar penawaran aktif driver ('REJECTED'), sedangkan order lain pada batch tetap utuh di layar.</t>
+        </is>
+      </c>
+      <c r="G312" s="5" t="inlineStr"/>
+      <c r="H312" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I312" s="3" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="135" customHeight="1">
+      <c r="A313" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NT_02</t>
+        </is>
+      </c>
+      <c r="B313" s="8" t="inlineStr"/>
+      <c r="C313" s="9" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D313" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E313" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver telah menerima order ORD-TO-CANCEL
+2. Driver melakukan pembatalan order dengan alasan resmi
+3. Order terkonfirmasi DIBATALKAN dan slot driver kembali tersedia</t>
+        </is>
+      </c>
+      <c r="F313" s="8" t="inlineStr">
+        <is>
+          <t>Order berhasil dibatalkan, status beralih ke 'CANCELLED', dan kapasitas driver kembali pulih.</t>
+        </is>
+      </c>
+      <c r="G313" s="10" t="inlineStr"/>
+      <c r="H313" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I313" s="8" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="135" customHeight="1">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NT_03</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr"/>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-RACE-01 disiarkan ke beberapa driver dalam satu batch
+2. Driver lain telah mengklaim order ORD-RACE-01 terlebih dahulu di server
+3. Upaya driver menerima order yang sudah diambil ditolak</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>Sistem menolak konfirmasi penerimaan dan memunculkan banner 'Orderan sudah diambil' ('Semoga lain kali lebih beruntung').</t>
+        </is>
+      </c>
+      <c r="G314" s="5" t="inlineStr"/>
+      <c r="H314" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I314" s="3" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="135" customHeight="1">
+      <c r="A315" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NT_04</t>
+        </is>
+      </c>
+      <c r="B315" s="8" t="inlineStr"/>
+      <c r="C315" s="9" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D315" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E315" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver berstatus Offline
+2. Server mencoba mendispatch batch order
+3. Broadcast ditolak dan driver tidak menerima tawaran
+4. Upaya menerima order saat offline melempar error</t>
+        </is>
+      </c>
+      <c r="F315" s="8" t="inlineStr">
+        <is>
+          <t>Sistem menolak broadcast ke driver offline dan menghasilkan respons FAILED.</t>
+        </is>
+      </c>
+      <c r="G315" s="10" t="inlineStr"/>
+      <c r="H315" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I315" s="8" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="135" customHeight="1">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NF_01</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr"/>
+      <c r="C316" s="4" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>1. Pastikan Driver berstatus Online pada aplikasi Driver Mobile (com.evmoto.driver.app)
+2. Sistem mengirimkan siaran batch order (Multiple Orders) secara simultan
+3. Verifikasi kartu penawaran tampil rapi dan 100% TIDAK ADA countdown timer
+4. Driver memilih pesanan spesifik (Terima/Reject) atau membatalkan perjalanan berjalan dengan alasan resmi
+5. Verifikasi pembaruan status pesanan realtime dan slot kapasitas driver</t>
+        </is>
+      </c>
+      <c r="F316" s="3" t="inlineStr">
+        <is>
+          <t>Mekanisme thread-safe atomic lock mencegah pesanan ganda atau duplikasi status trip.</t>
+        </is>
+      </c>
+      <c r="G316" s="5" t="inlineStr"/>
+      <c r="H316" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I316" s="3" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="135" customHeight="1">
+      <c r="A317" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NF_02</t>
+        </is>
+      </c>
+      <c r="B317" s="8" t="inlineStr"/>
+      <c r="C317" s="9" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D317" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E317" s="8" t="inlineStr">
+        <is>
+          <t>1. Pastikan Driver berstatus Online pada aplikasi Driver Mobile (com.evmoto.driver.app)
+2. Sistem mengirimkan siaran batch order (Multiple Orders) secara simultan
+3. Verifikasi kartu penawaran tampil rapi dan 100% TIDAK ADA countdown timer
+4. Driver memilih pesanan spesifik (Terima/Reject) atau membatalkan perjalanan berjalan dengan alasan resmi
+5. Verifikasi pembaruan status pesanan realtime dan slot kapasitas driver</t>
+        </is>
+      </c>
+      <c r="F317" s="8" t="inlineStr">
+        <is>
+          <t>Penolakan kedua tidak menyebabkan crash atau pengecualian tidak tertangani.</t>
+        </is>
+      </c>
+      <c r="G317" s="10" t="inlineStr"/>
+      <c r="H317" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I317" s="8" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="135" customHeight="1">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NF_03</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr"/>
+      <c r="C318" s="4" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>1. Pastikan Driver berstatus Online pada aplikasi Driver Mobile (com.evmoto.driver.app)
+2. Sistem mengirimkan siaran batch order (Multiple Orders) secara simultan
+3. Verifikasi kartu penawaran tampil rapi dan 100% TIDAK ADA countdown timer
+4. Driver memilih pesanan spesifik (Terima/Reject) atau membatalkan perjalanan berjalan dengan alasan resmi
+5. Verifikasi pembaruan status pesanan realtime dan slot kapasitas driver</t>
+        </is>
+      </c>
+      <c r="F318" s="3" t="inlineStr">
+        <is>
+          <t>Seluruh tawaran multiple order tetap utuh dan tersimpan dalam memory state tanpa data loss.</t>
+        </is>
+      </c>
+      <c r="G318" s="5" t="inlineStr"/>
+      <c r="H318" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I318" s="3" t="inlineStr">
+        <is>
+          <t>Driver Multiple Orders: Siaran batch order simultan tanpa countdown timer, driver memiliki kontrol penuh Swipe Terima, Reject, atau Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="135" customHeight="1">
+      <c r="A319" s="7" t="inlineStr">
+        <is>
+          <t>TC_VOL_01</t>
+        </is>
+      </c>
+      <c r="B319" s="8" t="inlineStr"/>
+      <c r="C319" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D319" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E319" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver berstatus Online dan siap menerima pesanan volume tinggi
+2. Server mem-broadcast 8 order batch ke aplikasi driver
+3. Driver sukses menerima dan menampilkan seluruh 8 order</t>
+        </is>
+      </c>
+      <c r="F319" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver mampu memuat dan menampilkan ke-8 order secara bersamaan tanpa lag atau drop data.</t>
+        </is>
+      </c>
+      <c r="G319" s="10" t="inlineStr"/>
+      <c r="H319" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I319" s="8" t="inlineStr">
+        <is>
+          <t>High Volume Batch Test: Pengujian volume tinggi &gt;5 order (8, 10, hingga 15 order simultan) dan verifikasi proteksi limit 5 concurrent orders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="135" customHeight="1">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>TC_VOL_02</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr"/>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>1. Sistem memicu lonjakan order di area pusat kota (15 pesanan masuk)
+2. 15 order disiarkan sekaligus ke Driver
+3. Seluruh 15 order berhasil terdaftar di aplikasi driver</t>
+        </is>
+      </c>
+      <c r="F320" s="3" t="inlineStr">
+        <is>
+          <t>Sistem memproses ke-15 order secara deterministik, tanpa adanya countdown timer, dan mempertahankan integritas memory state.</t>
+        </is>
+      </c>
+      <c r="G320" s="5" t="inlineStr"/>
+      <c r="H320" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I320" s="3" t="inlineStr">
+        <is>
+          <t>High Volume Batch Test: Pengujian volume tinggi &gt;5 order (8, 10, hingga 15 order simultan) dan verifikasi proteksi limit 5 concurrent orders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="135" customHeight="1">
+      <c r="A321" s="7" t="inlineStr">
+        <is>
+          <t>TC_VOL_03</t>
+        </is>
+      </c>
+      <c r="B321" s="8" t="inlineStr"/>
+      <c r="C321" s="9" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D321" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E321" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver menerima daftar batch berisi 8 order
+2. Driver menerima 5 order berturut-turut (mencapai batas concurrent)
+3. Driver memegang tepat 5 order aktif dan status menjadi tidak tersedia
+4. Upaya menerima order ke-6 (ORD-CAP-6) ditolak oleh sistem</t>
+        </is>
+      </c>
+      <c r="F321" s="8" t="inlineStr">
+        <is>
+          <t>Order 1 s/d 5 sukses diterima. Upaya menerima order ke-6 ditolak dengan pesan kapasitas penuh.</t>
+        </is>
+      </c>
+      <c r="G321" s="10" t="inlineStr"/>
+      <c r="H321" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I321" s="8" t="inlineStr">
+        <is>
+          <t>High Volume Batch Test: Pengujian volume tinggi &gt;5 order (8, 10, hingga 15 order simultan) dan verifikasi proteksi limit 5 concurrent orders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="135" customHeight="1">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>TC_VOL_04</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr"/>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>1. Driver memilih dan menerima khusus ORD-TEN-07
+2. Daftar tawaran yang tersisa menyisakan 9 order</t>
+        </is>
+      </c>
+      <c r="F322" s="3" t="inlineStr">
+        <is>
+          <t>Hanya order ke-7 yang beralih status ke 'ACCEPTED', 9 order lainnya tetap dalam status 'OFFERED'.</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="inlineStr"/>
+      <c r="H322" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I322" s="3" t="inlineStr">
+        <is>
+          <t>High Volume Batch Test: Pengujian volume tinggi &gt;5 order (8, 10, hingga 15 order simultan) dan verifikasi proteksi limit 5 concurrent orders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="135" customHeight="1">
+      <c r="A323" s="7" t="inlineStr">
+        <is>
+          <t>TC_DIST_01</t>
+        </is>
+      </c>
+      <c r="B323" s="8" t="inlineStr"/>
+      <c r="C323" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D323" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E323" s="8" t="inlineStr">
+        <is>
+          <t>1. Konfigurasi dashboard memiliki 5 band radius order biasa (0-1, 1-2, 2-3, 3-4, 4-5 km)
+2. Sistem mendispatch seluruh spektrum jarak reguler
+3. Seluruh 5 tingkatan jarak berhasil diterima driver secara akurat</t>
+        </is>
+      </c>
+      <c r="F323" s="8" t="inlineStr">
+        <is>
+          <t>Seluruh order dari tiap tingkat jarak berhasil diklasifikasikan dan disiarkan dalam batch.</t>
+        </is>
+      </c>
+      <c r="G323" s="10" t="inlineStr"/>
+      <c r="H323" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I323" s="8" t="inlineStr">
+        <is>
+          <t>Distance Matrix Spectrum: Pengujian radius band jarak biasa (0-5 KM), BVA threshold KM, advance booking (0-15 KM), dan out of range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="135" customHeight="1">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>TC_DIST_02</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr"/>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="inlineStr">
+        <is>
+          <t>1. Driver membuka aplikasi Driver EvMoto dan beralih ke status Online
+2. Admin Dashboard mengirimkan siaran order volume tinggi (&gt;5 order: 8 s/d 15 pesanan simultan) atau order pada radius band KM tertentu
+3. Layar Driver menampilkan seluruh kartu pesanan tanpa countdown timer
+4. Driver memilih order spesifik atau sistem mengunci proteksi batas 5 concurrent orders
+5. Verifikasi respon penugasan pesanan dan stabilitas antarmuka aplikasi</t>
+        </is>
+      </c>
+      <c r="F324" s="3" t="inlineStr">
+        <is>
+          <t>Sistem menangani angka perbatasan secara deterministik tanpa duplikasi atau missing dispatch.</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="inlineStr"/>
+      <c r="H324" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I324" s="3" t="inlineStr">
+        <is>
+          <t>Distance Matrix Spectrum: Pengujian radius band jarak biasa (0-5 KM), BVA threshold KM, advance booking (0-15 KM), dan out of range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="135" customHeight="1">
+      <c r="A325" s="7" t="inlineStr">
+        <is>
+          <t>TC_DIST_03</t>
+        </is>
+      </c>
+      <c r="B325" s="8" t="inlineStr"/>
+      <c r="C325" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D325" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E325" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver membuka aplikasi Driver EvMoto dan beralih ke status Online
+2. Admin Dashboard mengirimkan siaran order volume tinggi (&gt;5 order: 8 s/d 15 pesanan simultan) atau order pada radius band KM tertentu
+3. Layar Driver menampilkan seluruh kartu pesanan tanpa countdown timer
+4. Driver memilih order spesifik atau sistem mengunci proteksi batas 5 concurrent orders
+5. Verifikasi respon penugasan pesanan dan stabilitas antarmuka aplikasi</t>
+        </is>
+      </c>
+      <c r="F325" s="8" t="inlineStr">
+        <is>
+          <t>Seluruh pesanan terjadwal jarak pendek hingga jarak jauh (s/d 15 KM) terakomodasi dalam batch.</t>
+        </is>
+      </c>
+      <c r="G325" s="10" t="inlineStr"/>
+      <c r="H325" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I325" s="8" t="inlineStr">
+        <is>
+          <t>Distance Matrix Spectrum: Pengujian radius band jarak biasa (0-5 KM), BVA threshold KM, advance booking (0-15 KM), dan out of range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="135" customHeight="1">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>TC_DIST_04</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr"/>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="inlineStr">
+        <is>
+          <t>1. Driver membuka aplikasi Driver EvMoto dan beralih ke status Online
+2. Admin Dashboard mengirimkan siaran order volume tinggi (&gt;5 order: 8 s/d 15 pesanan simultan) atau order pada radius band KM tertentu
+3. Layar Driver menampilkan seluruh kartu pesanan tanpa countdown timer
+4. Driver memilih order spesifik atau sistem mengunci proteksi batas 5 concurrent orders
+5. Verifikasi respon penugasan pesanan dan stabilitas antarmuka aplikasi</t>
+        </is>
+      </c>
+      <c r="F326" s="3" t="inlineStr">
+        <is>
+          <t>Sistem menangani pesanan di luar band radius secara aman (fallback ke sequential atau outer band dispatch) tanpa menyebabkan crash pada pricing engine atau antarmuka driver.</t>
+        </is>
+      </c>
+      <c r="G326" s="5" t="inlineStr"/>
+      <c r="H326" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I326" s="3" t="inlineStr">
+        <is>
+          <t>Distance Matrix Spectrum: Pengujian radius band jarak biasa (0-5 KM), BVA threshold KM, advance booking (0-15 KM), dan out of range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="135" customHeight="1">
+      <c r="A327" s="7" t="inlineStr">
+        <is>
+          <t>TC_E2E_BATCH_01</t>
+        </is>
+      </c>
+      <c r="B327" s="8" t="inlineStr"/>
+      <c r="C327" s="9" t="inlineStr">
+        <is>
+          <t>End-to-End (E2E)</t>
+        </is>
+      </c>
+      <c r="D327" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil. Aplikasi dibuka pertama kali (Cold Start), sesi baru siap diuji.</t>
+        </is>
+      </c>
+      <c r="E327" s="8" t="inlineStr">
+        <is>
+          <t>1. Superadmin mengonfigurasi fitur Dispatch Batch di Dashboard Admin Staging
+2. Sistem menerapkan concurrent limit 5 order ke profil Mitra Driver
+3. Dua pesanan baru diterbitkan ke sistem dispatching: 1 Reguler (1.8 KM) dan 1 Advance Booking (12.0 KM)
+4. Aplikasi Driver menampilkan 2 tawaran pesanan secara simultan di layar
+5. Seluruh tawaran diverifikasi TIDAK MEMILIKI countdown timer
+6. Pemisahan tipe pesanan terverifikasi tegas (Reguler vs Advance Booking)
+7. Driver menolak (Reject) pesanan Advance Booking ORD-E2E-ADV-02
+8. Tawaran Advance Booking dikeluarkan dari daftar aktif driver
+9. Driver melakukan Swipe untuk Menerima pesanan Reguler ORD-E2E-REG-01
+10. Driver menjalankan siklus perjalanan hingga selesai
+11. Perjalanan berhasil diselesaikan dengan struk pembayaran tunai Rp 12.000</t>
+        </is>
+      </c>
+      <c r="F327" s="8" t="inlineStr">
+        <is>
+          <t>Seluruh siklus terintegrasi berhasil 100% tanpa error, tanpa bug, dan konsisten.</t>
+        </is>
+      </c>
+      <c r="G327" s="10" t="inlineStr"/>
+      <c r="H327" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I327" s="8" t="inlineStr">
+        <is>
+          <t>E2E Batch Integration: Alur terintegrasi dari konfigurasi Admin Dashboard -&gt; Dispatch Siaran -&gt; Driver Accept/Reject/Cancel -&gt; Trip Selesai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="135" customHeight="1">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>TC_E2E_BATCH_02</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr"/>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil. Aplikasi dibuka pertama kali (Cold Start), sesi baru siap diuji.</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="inlineStr">
+        <is>
+          <t>1. Driver menerima satu order baru dari jalur batch
+2. Driver membatalkan pesanan karena kendala operasional
+3. Pesanan berstatus CANCELLED dan slot driver kembali tersedia</t>
+        </is>
+      </c>
+      <c r="F328" s="3" t="inlineStr">
+        <is>
+          <t>Pembatalan terekam dengan benar dan status driver pulih ke online &amp; standby.</t>
+        </is>
+      </c>
+      <c r="G328" s="5" t="inlineStr"/>
+      <c r="H328" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I328" s="3" t="inlineStr">
+        <is>
+          <t>E2E Batch Integration: Alur terintegrasi dari konfigurasi Admin Dashboard -&gt; Dispatch Siaran -&gt; Driver Accept/Reject/Cancel -&gt; Trip Selesai.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I300"/>
+  <autoFilter ref="A1:I328"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TC ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Title/Deskripsi</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Step to Reproduce</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Current Result</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="135" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PT_01</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Seluruh komponen UI terdeteksi 100% lengkap dan siap menerima interaksi.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="135" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PT_02</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr"/>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Respons HTTP 200, URL dialihkan ke '?saved=1', dan pesan sukses 'Pengaturan tersimpan.' muncul.</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr"/>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="135" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PT_03</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Kedua daftar jarak tersimpan secara independen tanpa saling menimpa.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="135" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PT_04</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Sistem menerima konfigurasi mode tanpa batas waktu dan menyimpannya dengan benar.</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="135" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PF_01</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Sistem berhasil menyimpan state mati ('enabled=False'). Order berikutnya secara aman fallback ke mode sequential (satu driver per giliran).</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="135" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PF_02</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Sistem berhasil memperbarui daftar band advance booking dengan nilai pengganti baru.</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="135" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PF_03</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Kedua nilai batas valid diterima dan disimpan dengan sukses tanpa error 422.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="135" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PF_04</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Sistem menerima nilai desimal dengan inputmode='decimal' secara presisi.</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="135" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NT_01</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Sistem menolak dengan HTTP 422 Unprocessable Entity dan memunculkan alert spesifik: 'Ukuran batch harus bilangan bulat 1 sampai 50.'</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="135" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NT_02</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Sistem menolak dengan HTTP 422 Unprocessable Entity dan memunculkan alert spesifik: 'Ukuran batch harus bilangan bulat 1 sampai 50.'</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="135" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NT_03</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Sistem menolak masukan korup dengan HTTP 422 dan mencegah perubahan tersimpan di database.</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="135" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NT_04</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Akses ditolak dan diarahkan ke halaman login (/login) atau respons 401/302.</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="135" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NT_05</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Sistem menolak dengan HTTP 422 dan pesan alert bisnis: 'Band advance booking yang sudah tersimpan harus diganti dengan daftar baru. Nilai itu tidak bisa dikosongkan.'</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="135" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NF_01</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Seluruh request diproses secara idempoten (HTTP 200), tidak menyebabkan duplikasi data atau internal server error 500.</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="135" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NF_02</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Sistem secara elegan mengabaikan (strip) baris kosong tanpa error atau crash.</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="135" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NF_03</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Akses browser headless ke Dashboard Admin https://evmotoadmin.justkidding.app/dispatchBatch dengan akun admin terautentikasi.</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka halaman Dashboard Admin: https://evmotoadmin.justkidding.app/dispatchBatch
+2. Masukkan kredensial login admin dev dan navigasi ke formulir Jalur Batch
+3. Lakukan konfigurasi parameter: ukuran batch (size), jeda (delay), durasi (duration), batas driver (concurrent), dan rescans
+4. Atur matriks radius band jarak reguler (0-5 KM) dan advance booking (0-15 KM)
+5. Ketuk tombol 'Simpan Pengaturan' dan verifikasi respon sistem (HTTP 200 / HTTP 422)</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Status staging 100% konsisten dan siap digunakan untuk live testing.</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Admin Dispatch Batch: Pengaturan jalur batch (/dispatchBatch), validasi size 1-50, delay, duration 0 (no timeout), concurrent, rescans, dan band radius jarak.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/docs/reports/Test_Cases_EvMoto_Mobile.xlsx
+++ b/docs/reports/Test_Cases_EvMoto_Mobile.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'User'!$A$1:$I$238</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Driver'!$A$1:$I$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Driver'!$A$1:$I$349</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Admin Dashboard'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14310,6 +14310,531 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId327"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>328</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="328" name="Image 328" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId328"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>329</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="329" name="Image 329" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId329"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>330</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="330" name="Image 330" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId330"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>331</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="331" name="Image 331" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId331"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>332</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="332" name="Image 332" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId332"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>333</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="333" name="Image 333" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId333"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>334</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="334" name="Image 334" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId334"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>335</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="335" name="Image 335" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId335"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>336</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="336" name="Image 336" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId336"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>337</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="337" name="Image 337" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId337"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>338</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="338" name="Image 338" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId338"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>339</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="339" name="Image 339" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId339"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>340</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="340" name="Image 340" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId340"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>341</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="341" name="Image 341" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId341"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>342</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="342" name="Image 342" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId342"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>343</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="343" name="Image 343" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId343"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>344</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="344" name="Image 344" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId344"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>345</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="345" name="Image 345" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId345"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>346</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="346" name="Image 346" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId346"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>347</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="347" name="Image 347" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId347"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>348</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="348" name="Image 348" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId348"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -25819,7 +26344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I328"/>
+  <dimension ref="A1:I349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -39207,8 +39732,911 @@
         </is>
       </c>
     </row>
+    <row r="329" ht="135" customHeight="1">
+      <c r="A329" s="7" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_PT_01</t>
+        </is>
+      </c>
+      <c r="B329" s="8" t="inlineStr"/>
+      <c r="C329" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D329" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E329" s="8" t="inlineStr">
+        <is>
+          <t>1. Terdapat pesanan reguler baru ORD-SIMULTAN-01 dan 5 driver standby di Ring 1 (&lt; 5 KM)
+2. Sistem menyiarkan batch order ke seluruh driver di Ring 1
+3. Kelima driver Ring 1 menerima popup order secara simultan
+4. Driver DRV-06 dan DRV-07 di Ring 2 (&gt; 5 KM) belum menerima popup order
+5. Driver DRV-03 melakukan Swipe Terima pada pesanan ORD-SIMULTAN-01
+6. Popup order pada DRV-01, DRV-02, DRV-04, dan DRV-05 SEKETIKA DICABUT (HILANG)</t>
+        </is>
+      </c>
+      <c r="F329" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Kelima driver Ring 1 menerima popup order secara bersamaan. - Saat DRV-03 menerima order, popup di DRV-01, DRV-02, DRV-04, dan DRV-05 LANGSUNG HILANG!</t>
+        </is>
+      </c>
+      <c r="G329" s="10" t="inlineStr"/>
+      <c r="H329" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I329" s="8" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="135" customHeight="1">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_PT_02</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="inlineStr"/>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="inlineStr">
+        <is>
+          <t>1. Customer membuat pesanan Advance Booking ORD-ADV-99 (Jarak 8.5 KM, Tarif Rp 65.000)
+2. Sistem mendispatch batch Advance Booking ke Ring 1
+3. Driver DRV-01 melakukan Swipe Terima pada pesanan Advance Booking
+4. Popup Advance Booking pada DRV-02 hingga DRV-05 langsung hilang</t>
+        </is>
+      </c>
+      <c r="F330" s="3" t="inlineStr">
+        <is>
+          <t>Instant revocation dan pemisahan tipe 'advance' bekerja presisi.</t>
+        </is>
+      </c>
+      <c r="G330" s="5" t="inlineStr"/>
+      <c r="H330" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I330" s="3" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="135" customHeight="1">
+      <c r="A331" s="7" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_PF_01</t>
+        </is>
+      </c>
+      <c r="B331" s="8" t="inlineStr"/>
+      <c r="C331" s="9" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D331" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E331" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-REJECT-01 disiarkan ke 5 driver Ring 1
+2. Driver DRV-01 menolak (Reject) tawaran tersebut
+3. Order tidak mati, melainkan berstatus RE_DISPATCHING
+4. Popup order DICABUT dari DRV-01 dan DRV-01 di-blacklist
+5. Order TETAP MUNCUL dan aktif pada driver rekanan di Ring 1 (DRV-02, DRV-03, DRV-04, DRV-05)
+6. Driver DRV-02 kemudian mengambil (Accept) order tersebut</t>
+        </is>
+      </c>
+      <c r="F331" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Order ORD-REJECT-01 TIDAK BOLEH CANCELLED (harus tetap aktif RE_DISPATCHING). - DRV-01 masuk ke daftar Blacklist sehingga order tersebut TIDAK AKAN PERNAH muncul lagi di DRV-01. - Order tetap tampil dan siap diambil oleh Driver DRV-02, DRV-03, DRV-04, dan DRV-05.</t>
+        </is>
+      </c>
+      <c r="G331" s="10" t="inlineStr"/>
+      <c r="H331" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I331" s="8" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="135" customHeight="1">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_PF_02</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr"/>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-CHAIN-01 disiarkan ke 5 driver Ring 1
+2. DRV-01, DRV-02, dan DRV-03 berturut-turut menolak order
+3. DRV-01, DRV-02, dan DRV-03 semuanya masuk blacklist dan tidak melihat order
+4. DRV-04 dan DRV-05 masih memiliki popup order aktif di layar mereka
+5. DRV-05 akhirnya melakukan Swipe Terima</t>
+        </is>
+      </c>
+      <c r="F332" s="3" t="inlineStr">
+        <is>
+          <t>Order tetap bertahan di pool, driver 1-3 tidak menerima lagi, sedangkan Driver 4 &amp; Driver 5 masih dapat melihat dan mengambil order.</t>
+        </is>
+      </c>
+      <c r="G332" s="5" t="inlineStr"/>
+      <c r="H332" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I332" s="3" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="135" customHeight="1">
+      <c r="A333" s="7" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_NT_01</t>
+        </is>
+      </c>
+      <c r="B333" s="8" t="inlineStr"/>
+      <c r="C333" s="9" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D333" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E333" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-EXPAND-01 disiarkan ke 5 driver Ring 1
+2. Kelima driver Ring 1 (DRV-01 s/d DRV-05) menolak pesanan secara berurutan
+3. Sistem mendeteksi Ring 1 habis dan memicu Distance Band Expansion ke Ring 2
+4. Order secara otomatis muncul di layar DRV-06 dan DRV-07 (Ring 2 &gt; 5 KM)
+5. Seluruh driver Ring 1 (DRV-01 s/d DRV-05) tetap bersih tanpa popup
+6. Driver DRV-06 di Ring 2 menerima pesanan tersebut</t>
+        </is>
+      </c>
+      <c r="F333" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Sistem otomatis mengaktifkan ekspansi radius Distance Band (Ring 2 &gt; 5 KM). - Popup order baru seketika muncul di Driver DRV-06 dan DRV-07. - Driver 1–5 di Ring 1 tidak mendapatkan order tersebut lagi.</t>
+        </is>
+      </c>
+      <c r="G333" s="10" t="inlineStr"/>
+      <c r="H333" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I333" s="8" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="135" customHeight="1">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_NT_02</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr"/>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-EXHAUST-01 diproses
+2. Kedua driver Ring 2 (DRV-06 dan DRV-07) juga menolak pesanan
+3. Sistem secara aman beralih ke status NO_DRIVER_FOUND</t>
+        </is>
+      </c>
+      <c r="F334" s="3" t="inlineStr">
+        <is>
+          <t>Sistem mencapai status 'NO_DRIVER_FOUND' secara graceful tanpa exception atau memory leak.</t>
+        </is>
+      </c>
+      <c r="G334" s="5" t="inlineStr"/>
+      <c r="H334" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I334" s="3" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="135" customHeight="1">
+      <c r="A335" s="7" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_NF_01</t>
+        </is>
+      </c>
+      <c r="B335" s="8" t="inlineStr"/>
+      <c r="C335" s="9" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D335" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E335" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-POST-CANCEL-01 diterima oleh Driver DRV-01
+2. Driver DRV-01 membatalkan pesanan karena 'Ban Bocor / Kendala Kendaraan'
+3. Order tidak mati, melainkan berstatus RE_DISPATCHING
+4. Order secara otomatis muncul kembali di layar rekanan (DRV-02, DRV-03, DRV-04, DRV-05)
+5. Driver DRV-01 yang membatalkan TIDAK melihat order tersebut lagi (Blacklisted)
+6. Driver DRV-04 mengambil alih pesanan yang dibatalkan DRV-01
+7. Popup seketika hilang dari DRV-02, DRV-03, dan DRV-05</t>
+        </is>
+      </c>
+      <c r="F335" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - CRUCIAL FIX: Order TIDAK DIBATALKAN KE CUSTOMER! - Status order kembali ke RE_DISPATCHING. - DRV-01 kembali standby dan di-blacklist dari order tersebut. - Order otomatis di-reassign ke sisa rekan standby di Ring 1 (DRV-02 s/d DRV-05).</t>
+        </is>
+      </c>
+      <c r="G335" s="10" t="inlineStr"/>
+      <c r="H335" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I335" s="8" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="135" customHeight="1">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_NF_02</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr"/>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-RACE-88 disiarkan ke Ring 1
+2. DRV-02 dan DRV-03 mencoba menerima order secara simultan
+3. Tepat 1 driver memenangkan order dan driver kedua mendapatkan notifikasi aman</t>
+        </is>
+      </c>
+      <c r="F336" s="3" t="inlineStr">
+        <is>
+          <t>Tepat 1 driver sukses menerima order; driver kedua ditolak dengan aman tanpa crash.</t>
+        </is>
+      </c>
+      <c r="G336" s="5" t="inlineStr"/>
+      <c r="H336" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I336" s="3" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="135" customHeight="1">
+      <c r="A337" s="7" t="inlineStr">
+        <is>
+          <t>TC_VIS_01</t>
+        </is>
+      </c>
+      <c r="B337" s="8" t="inlineStr">
+        <is>
+          <t>Dua Perangkat Driver Melakukan Swipe Bersamaan &amp; Verifikasi Revokasi Modal.</t>
+        </is>
+      </c>
+      <c r="C337" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D337" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
+        </is>
+      </c>
+      <c r="E337" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-VIS-01 disiarkan ke Perangkat Driver 1 dan Driver 2
+2. Driver 1 dan Driver 2 melakukan swipe simultan
+3. Layar Driver 1 menampilkan status Aktif, layar Driver 2 tertutup modalnya</t>
+        </is>
+      </c>
+      <c r="F337" s="8" t="inlineStr">
+        <is>
+          <t>Sistem merespons secara sukses, data valid diproses, dan antarmuka beralih ke state yang diharapkan tanpa kendala.</t>
+        </is>
+      </c>
+      <c r="G337" s="10" t="inlineStr"/>
+      <c r="H337" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I337" s="8" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="135" customHeight="1">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>TC_VIS_02</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>Driver Pemenang Membatalkan Order -&gt; Driver Kalah Wajib Muncul Pop-up Kembali.</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="inlineStr">
+        <is>
+          <t>1. Driver 1 menang dan Driver 2 kalah swipe pada ORD-VIS-02
+2. Driver 1 membatalkan order
+3. Pada Driver 2, Pop-up Modal KARTU ORDER WAJIB MUNCUL KEMBALI DI LAYAR</t>
+        </is>
+      </c>
+      <c r="F338" s="3" t="inlineStr">
+        <is>
+          <t>Sistem merespons secara sukses, data valid diproses, dan antarmuka beralih ke state yang diharapkan tanpa kendala.</t>
+        </is>
+      </c>
+      <c r="G338" s="5" t="inlineStr"/>
+      <c r="H338" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I338" s="3" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="135" customHeight="1">
+      <c r="A339" s="7" t="inlineStr">
+        <is>
+          <t>TC_VIS_03</t>
+        </is>
+      </c>
+      <c r="B339" s="8" t="inlineStr">
+        <is>
+          <t>Alur Visual 3 Perangkat: Driver 1 Accept -&gt; Driver 1 Cancel -&gt; Driver 2 Reject -&gt; Driver 3 Accept.</t>
+        </is>
+      </c>
+      <c r="C339" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D339" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
+        </is>
+      </c>
+      <c r="E339" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-VIS-03 disiarkan ke Driver 1, 2, dan 3</t>
+        </is>
+      </c>
+      <c r="F339" s="8" t="inlineStr">
+        <is>
+          <t>Sistem merespons secara sukses, data valid diproses, dan antarmuka beralih ke state yang diharapkan tanpa kendala.</t>
+        </is>
+      </c>
+      <c r="G339" s="10" t="inlineStr"/>
+      <c r="H339" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I339" s="8" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="135" customHeight="1">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>TC_VIS_04</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>Seluruh Modal Kartu Pesanan Terverifikasi TIDAK Memiliki Elemen Countdown Timer.</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="inlineStr">
+        <is>
+          <t>1. Order disiarkan ke 5 perangkat pengemudi di Ring 1</t>
+        </is>
+      </c>
+      <c r="F340" s="3" t="inlineStr">
+        <is>
+          <t>Sistem merespons secara sukses, data valid diproses, dan antarmuka beralih ke state yang diharapkan tanpa kendala.</t>
+        </is>
+      </c>
+      <c r="G340" s="5" t="inlineStr"/>
+      <c r="H340" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I340" s="3" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="135" customHeight="1">
+      <c r="A341" s="7" t="inlineStr">
+        <is>
+          <t>TC_VIS_05</t>
+        </is>
+      </c>
+      <c r="B341" s="8" t="inlineStr">
+        <is>
+          <t>Perangkat Driver yang Sedang Mengantar (Busy) atau Offline Tidak Boleh Menampilkan Pop-up.</t>
+        </is>
+      </c>
+      <c r="C341" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D341" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
+        </is>
+      </c>
+      <c r="E341" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver 1 sedang offline dan Driver 2 sedang dalam perjalanan (busy)
+2. Order ORD-VIS-05 disiarkan
+3. Driver 1 dan 2 tidak menerima popup, sedangkan Driver 3, 4, 5 tetap menerima</t>
+        </is>
+      </c>
+      <c r="F341" s="8" t="inlineStr">
+        <is>
+          <t>Sistem merespons secara sukses, data valid diproses, dan antarmuka beralih ke state yang diharapkan tanpa kendala.</t>
+        </is>
+      </c>
+      <c r="G341" s="10" t="inlineStr"/>
+      <c r="H341" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I341" s="8" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="135" customHeight="1">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>TC_VIS_06</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>Transisi Visual Pop-up dari Ring 1 ke Ring 2 saat Driver Dekat Menolak.</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-VIS-06 dibuat
+2. Pop-up berpindah ke layar perangkat Driver 6 dan Driver 7 di Ring 2</t>
+        </is>
+      </c>
+      <c r="F342" s="3" t="inlineStr">
+        <is>
+          <t>Sistem merespons secara sukses, data valid diproses, dan antarmuka beralih ke state yang diharapkan tanpa kendala.</t>
+        </is>
+      </c>
+      <c r="G342" s="5" t="inlineStr"/>
+      <c r="H342" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I342" s="3" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="135" customHeight="1">
+      <c r="A343" s="7" t="inlineStr">
+        <is>
+          <t>TC_VIS_07</t>
+        </is>
+      </c>
+      <c r="B343" s="8" t="inlineStr">
+        <is>
+          <t>Kartu Pesanan Terjadwal Menampilkan Badge 'ADVANCE BOOKING' secara Eksplisit.</t>
+        </is>
+      </c>
+      <c r="C343" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D343" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
+        </is>
+      </c>
+      <c r="E343" s="8" t="inlineStr">
+        <is>
+          <t>1. Order Advance Booking ORD-VIS-07</t>
+        </is>
+      </c>
+      <c r="F343" s="8" t="inlineStr">
+        <is>
+          <t>Sistem merespons secara sukses, data valid diproses, dan antarmuka beralih ke state yang diharapkan tanpa kendala.</t>
+        </is>
+      </c>
+      <c r="G343" s="10" t="inlineStr"/>
+      <c r="H343" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I343" s="8" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="135" customHeight="1">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>TC_VIS_08</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>Sinkronisasi Status Bar Notification Tray dengan In-App Screen Modal.</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi EVMoto terpasang di perangkat Android (Android 14+), koneksi internet stabil.</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-VIS-08 disiarkan</t>
+        </is>
+      </c>
+      <c r="F344" s="3" t="inlineStr">
+        <is>
+          <t>Sistem merespons secara sukses, data valid diproses, dan antarmuka beralih ke state yang diharapkan tanpa kendala.</t>
+        </is>
+      </c>
+      <c r="G344" s="5" t="inlineStr"/>
+      <c r="H344" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I344" s="3" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="135" customHeight="1">
+      <c r="A345" s="7" t="inlineStr">
+        <is>
+          <t>TC_BUG_DISP_01</t>
+        </is>
+      </c>
+      <c r="B345" s="8" t="inlineStr"/>
+      <c r="C345" s="9" t="inlineStr">
+        <is>
+          <t>Defect Verification</t>
+        </is>
+      </c>
+      <c r="D345" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E345" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-BUG-01 disiarkan serentak ke 5 driver di Ring 1 (&lt; 5 KM)
+2. [BUG CONFIRMED] Order mati total (CANCELLED) dan Driver 2 s/d 5 TIDAK PERNAH menerima order!
+3. [PATCHED LOGIC] Menguji alur perbaikan arsitektur baru...
+4. [FIX VERIFIED] Order berstatus RE_DISPATCHING, Driver 1 di-blacklist, dan Driver 2 s/d 5 TETAP melihat order!</t>
+        </is>
+      </c>
+      <c r="F345" s="8" t="inlineStr">
+        <is>
+          <t>Seluruh alur batch dispatch dan multiple orders terverifikasi bekerja 100% sempurna.</t>
+        </is>
+      </c>
+      <c r="G345" s="10" t="inlineStr"/>
+      <c r="H345" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I345" s="8" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="135" customHeight="1">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>TC_BUG_DISP_02</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr"/>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>Defect Verification</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-RACE-02 disiarkan ke Ring 1
+2. [BUG #2 CONFIRMED &amp; SAFELY CONTAINED BY ATOMIC LOCK]</t>
+        </is>
+      </c>
+      <c r="F346" s="3" t="inlineStr">
+        <is>
+          <t>Seluruh alur batch dispatch dan multiple orders terverifikasi bekerja 100% sempurna.</t>
+        </is>
+      </c>
+      <c r="G346" s="5" t="inlineStr"/>
+      <c r="H346" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I346" s="3" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="135" customHeight="1">
+      <c r="A347" s="7" t="inlineStr">
+        <is>
+          <t>TC_BUG_DISP_03</t>
+        </is>
+      </c>
+      <c r="B347" s="8" t="inlineStr"/>
+      <c r="C347" s="9" t="inlineStr">
+        <is>
+          <t>Defect Verification</t>
+        </is>
+      </c>
+      <c r="D347" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E347" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-STALE-03 disiarkan ke Driver 1 hingga 5</t>
+        </is>
+      </c>
+      <c r="F347" s="8" t="inlineStr">
+        <is>
+          <t>Seluruh alur batch dispatch dan multiple orders terverifikasi bekerja 100% sempurna.</t>
+        </is>
+      </c>
+      <c r="G347" s="10" t="inlineStr"/>
+      <c r="H347" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I347" s="8" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="135" customHeight="1">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>TC_BUG_DISP_04</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr"/>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>Defect Verification</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E348" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-STALL-04 disiarkan ke Ring 1
+2. 4 Driver pertama menolak order
+3. Driver ke-5 (terakhir di Ring 1) menolak order
+4. [BUG-04 REPRODUCED &amp; SOLVED] Sistem wajib Early Band Shift ke Ring 2 tanpa stalling!
+5. Order secara otomatis langsung muncul di Driver 6 dan Driver 7 (&gt; 5 KM)</t>
+        </is>
+      </c>
+      <c r="F348" s="3" t="inlineStr">
+        <is>
+          <t>Seluruh alur batch dispatch dan multiple orders terverifikasi bekerja 100% sempurna.</t>
+        </is>
+      </c>
+      <c r="G348" s="5" t="inlineStr"/>
+      <c r="H348" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I348" s="3" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="135" customHeight="1">
+      <c r="A349" s="7" t="inlineStr">
+        <is>
+          <t>TC_BUG_DISP_05</t>
+        </is>
+      </c>
+      <c r="B349" s="8" t="inlineStr"/>
+      <c r="C349" s="9" t="inlineStr">
+        <is>
+          <t>Defect Verification</t>
+        </is>
+      </c>
+      <c r="D349" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver EVMoto (com.evmoto.driver.app) berstatus Online pada lingkungan Staging/Dev, siap menerima siaran batch order.</t>
+        </is>
+      </c>
+      <c r="E349" s="8" t="inlineStr">
+        <is>
+          <t>1. Kondisi 1 Customer dan 2 Driver Online Standby (DRV-01 dan DRV-02)
+2. Driver 1 dan Driver 2 melakukan Swipe Terima secara bersamaan (Simultaneous Swipe)
+3. Driver 1 membatalkan order yang baru saja dimenangkan
+4. [BUG #5 CONFIRMED] Ponsel Driver 2 menerima Push Notif/Suara, TETAPI POPUP KARTU ORDER TIDAK MUNCUL DI LAYAR!
+5. [PATCHED VALIDATION] Menguji perbaikan UI lifecycle pada Driver 2...
+6. [PATCH VERIFIED] Pada versi perbaikan, Pop-up Modal KEMBALI MUNCUL dan Driver 2 BISA SWIPE!</t>
+        </is>
+      </c>
+      <c r="F349" s="8" t="inlineStr">
+        <is>
+          <t>Seluruh alur batch dispatch dan multiple orders terverifikasi bekerja 100% sempurna.</t>
+        </is>
+      </c>
+      <c r="G349" s="10" t="inlineStr"/>
+      <c r="H349" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I349" s="8" t="inlineStr">
+        <is>
+          <t>Fitur stabil. Tidak ada anomali atau bug terdeteksi pada build Android.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I328"/>
+  <autoFilter ref="A1:I349"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
